--- a/data/raw/wpi.xlsx
+++ b/data/raw/wpi.xlsx
@@ -17,89 +17,89 @@
     <sheet name="Enquiries" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="A2603039T">Data1!$B$1:$B$10,Data1!$B$11:$B$124</definedName>
-    <definedName name="A2603039T_Data">Data1!$B$11:$B$124</definedName>
-    <definedName name="A2603039T_Latest">Data1!$B$124</definedName>
-    <definedName name="A2603040A">Data1!$K$1:$K$10,Data1!$K$11:$K$124</definedName>
-    <definedName name="A2603040A_Data">Data1!$K$11:$K$124</definedName>
-    <definedName name="A2603040A_Latest">Data1!$K$124</definedName>
-    <definedName name="A2603041C">Data1!$T$1:$T$10,Data1!$T$11:$T$124</definedName>
-    <definedName name="A2603041C_Data">Data1!$T$11:$T$124</definedName>
-    <definedName name="A2603041C_Latest">Data1!$T$124</definedName>
-    <definedName name="A2603609J">Data1!$D$1:$D$10,Data1!$D$11:$D$124</definedName>
-    <definedName name="A2603609J_Data">Data1!$D$11:$D$124</definedName>
-    <definedName name="A2603609J_Latest">Data1!$D$124</definedName>
-    <definedName name="A2603610T">Data1!$M$1:$M$10,Data1!$M$11:$M$124</definedName>
-    <definedName name="A2603610T_Data">Data1!$M$11:$M$124</definedName>
-    <definedName name="A2603610T_Latest">Data1!$M$124</definedName>
-    <definedName name="A2603611V">Data1!$V$1:$V$10,Data1!$V$11:$V$124</definedName>
-    <definedName name="A2603611V_Data">Data1!$V$11:$V$124</definedName>
-    <definedName name="A2603611V_Latest">Data1!$V$124</definedName>
-    <definedName name="A2603989W">Data1!$C$1:$C$10,Data1!$C$11:$C$124</definedName>
-    <definedName name="A2603989W_Data">Data1!$C$11:$C$124</definedName>
-    <definedName name="A2603989W_Latest">Data1!$C$124</definedName>
-    <definedName name="A2603990F">Data1!$L$1:$L$10,Data1!$L$11:$L$124</definedName>
-    <definedName name="A2603990F_Data">Data1!$L$11:$L$124</definedName>
-    <definedName name="A2603990F_Latest">Data1!$L$124</definedName>
-    <definedName name="A2603991J">Data1!$U$1:$U$10,Data1!$U$11:$U$124</definedName>
-    <definedName name="A2603991J_Data">Data1!$U$11:$U$124</definedName>
-    <definedName name="A2603991J_Latest">Data1!$U$124</definedName>
-    <definedName name="A2713846W">Data1!$E$1:$E$10,Data1!$E$11:$E$124</definedName>
-    <definedName name="A2713846W_Data">Data1!$E$11:$E$124</definedName>
-    <definedName name="A2713846W_Latest">Data1!$E$124</definedName>
-    <definedName name="A2713848A">Data1!$H$1:$H$10,Data1!$H$11:$H$124</definedName>
-    <definedName name="A2713848A_Data">Data1!$H$11:$H$124</definedName>
-    <definedName name="A2713848A_Latest">Data1!$H$124</definedName>
-    <definedName name="A2713849C">Data1!$G$1:$G$10,Data1!$G$11:$G$124</definedName>
-    <definedName name="A2713849C_Data">Data1!$G$11:$G$124</definedName>
-    <definedName name="A2713849C_Latest">Data1!$G$124</definedName>
-    <definedName name="A2713851R">Data1!$J$1:$J$10,Data1!$J$11:$J$124</definedName>
-    <definedName name="A2713851R_Data">Data1!$J$11:$J$124</definedName>
-    <definedName name="A2713851R_Latest">Data1!$J$124</definedName>
-    <definedName name="A2713852T">Data1!$F$1:$F$10,Data1!$F$11:$F$124</definedName>
-    <definedName name="A2713852T_Data">Data1!$F$11:$F$124</definedName>
-    <definedName name="A2713852T_Latest">Data1!$F$124</definedName>
-    <definedName name="A2713854W">Data1!$I$1:$I$10,Data1!$I$11:$I$124</definedName>
-    <definedName name="A2713854W_Data">Data1!$I$11:$I$124</definedName>
-    <definedName name="A2713854W_Latest">Data1!$I$124</definedName>
-    <definedName name="A83895308K">Data1!$N$1:$N$10,Data1!$N$11:$N$124</definedName>
-    <definedName name="A83895308K_Data">Data1!$N$11:$N$124</definedName>
-    <definedName name="A83895308K_Latest">Data1!$N$124</definedName>
-    <definedName name="A83895309L">Data1!$W$1:$W$10,Data1!$W$11:$W$124</definedName>
-    <definedName name="A83895309L_Data">Data1!$W$11:$W$124</definedName>
-    <definedName name="A83895309L_Latest">Data1!$W$124</definedName>
-    <definedName name="A83895311X">Data1!$Q$1:$Q$10,Data1!$Q$11:$Q$124</definedName>
-    <definedName name="A83895311X_Data">Data1!$Q$11:$Q$124</definedName>
-    <definedName name="A83895311X_Latest">Data1!$Q$124</definedName>
-    <definedName name="A83895312A">Data1!$Z$1:$Z$10,Data1!$Z$11:$Z$124</definedName>
-    <definedName name="A83895312A_Data">Data1!$Z$11:$Z$124</definedName>
-    <definedName name="A83895312A_Latest">Data1!$Z$124</definedName>
-    <definedName name="A83895332K">Data1!$O$1:$O$10,Data1!$O$11:$O$124</definedName>
-    <definedName name="A83895332K_Data">Data1!$O$11:$O$124</definedName>
-    <definedName name="A83895332K_Latest">Data1!$O$124</definedName>
-    <definedName name="A83895333L">Data1!$X$1:$X$10,Data1!$X$11:$X$124</definedName>
-    <definedName name="A83895333L_Data">Data1!$X$11:$X$124</definedName>
-    <definedName name="A83895333L_Latest">Data1!$X$124</definedName>
-    <definedName name="A83895335T">Data1!$R$1:$R$10,Data1!$R$11:$R$124</definedName>
-    <definedName name="A83895335T_Data">Data1!$R$11:$R$124</definedName>
-    <definedName name="A83895335T_Latest">Data1!$R$124</definedName>
-    <definedName name="A83895336V">Data1!$AA$1:$AA$10,Data1!$AA$11:$AA$124</definedName>
-    <definedName name="A83895336V_Data">Data1!$AA$11:$AA$124</definedName>
-    <definedName name="A83895336V_Latest">Data1!$AA$124</definedName>
-    <definedName name="A83895395V">Data1!$P$1:$P$10,Data1!$P$11:$P$124</definedName>
-    <definedName name="A83895395V_Data">Data1!$P$11:$P$124</definedName>
-    <definedName name="A83895395V_Latest">Data1!$P$124</definedName>
-    <definedName name="A83895396W">Data1!$Y$1:$Y$10,Data1!$Y$11:$Y$124</definedName>
-    <definedName name="A83895396W_Data">Data1!$Y$11:$Y$124</definedName>
-    <definedName name="A83895396W_Latest">Data1!$Y$124</definedName>
-    <definedName name="A83895398A">Data1!$S$1:$S$10,Data1!$S$11:$S$124</definedName>
-    <definedName name="A83895398A_Data">Data1!$S$11:$S$124</definedName>
-    <definedName name="A83895398A_Latest">Data1!$S$124</definedName>
-    <definedName name="A83895399C">Data1!$AB$1:$AB$10,Data1!$AB$11:$AB$124</definedName>
-    <definedName name="A83895399C_Data">Data1!$AB$11:$AB$124</definedName>
-    <definedName name="A83895399C_Latest">Data1!$AB$124</definedName>
-    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$124</definedName>
-    <definedName name="Date_Range_Data">Data1!$A$11:$A$124</definedName>
+    <definedName name="A2603039T">Data1!$B$1:$B$10,Data1!$B$11:$B$125</definedName>
+    <definedName name="A2603039T_Data">Data1!$B$11:$B$125</definedName>
+    <definedName name="A2603039T_Latest">Data1!$B$125</definedName>
+    <definedName name="A2603040A">Data1!$K$1:$K$10,Data1!$K$11:$K$125</definedName>
+    <definedName name="A2603040A_Data">Data1!$K$11:$K$125</definedName>
+    <definedName name="A2603040A_Latest">Data1!$K$125</definedName>
+    <definedName name="A2603041C">Data1!$T$1:$T$10,Data1!$T$11:$T$125</definedName>
+    <definedName name="A2603041C_Data">Data1!$T$11:$T$125</definedName>
+    <definedName name="A2603041C_Latest">Data1!$T$125</definedName>
+    <definedName name="A2603609J">Data1!$D$1:$D$10,Data1!$D$11:$D$125</definedName>
+    <definedName name="A2603609J_Data">Data1!$D$11:$D$125</definedName>
+    <definedName name="A2603609J_Latest">Data1!$D$125</definedName>
+    <definedName name="A2603610T">Data1!$M$1:$M$10,Data1!$M$11:$M$125</definedName>
+    <definedName name="A2603610T_Data">Data1!$M$11:$M$125</definedName>
+    <definedName name="A2603610T_Latest">Data1!$M$125</definedName>
+    <definedName name="A2603611V">Data1!$V$1:$V$10,Data1!$V$11:$V$125</definedName>
+    <definedName name="A2603611V_Data">Data1!$V$11:$V$125</definedName>
+    <definedName name="A2603611V_Latest">Data1!$V$125</definedName>
+    <definedName name="A2603989W">Data1!$C$1:$C$10,Data1!$C$11:$C$125</definedName>
+    <definedName name="A2603989W_Data">Data1!$C$11:$C$125</definedName>
+    <definedName name="A2603989W_Latest">Data1!$C$125</definedName>
+    <definedName name="A2603990F">Data1!$L$1:$L$10,Data1!$L$11:$L$125</definedName>
+    <definedName name="A2603990F_Data">Data1!$L$11:$L$125</definedName>
+    <definedName name="A2603990F_Latest">Data1!$L$125</definedName>
+    <definedName name="A2603991J">Data1!$U$1:$U$10,Data1!$U$11:$U$125</definedName>
+    <definedName name="A2603991J_Data">Data1!$U$11:$U$125</definedName>
+    <definedName name="A2603991J_Latest">Data1!$U$125</definedName>
+    <definedName name="A2713846W">Data1!$E$1:$E$10,Data1!$E$11:$E$125</definedName>
+    <definedName name="A2713846W_Data">Data1!$E$11:$E$125</definedName>
+    <definedName name="A2713846W_Latest">Data1!$E$125</definedName>
+    <definedName name="A2713848A">Data1!$H$1:$H$10,Data1!$H$11:$H$125</definedName>
+    <definedName name="A2713848A_Data">Data1!$H$11:$H$125</definedName>
+    <definedName name="A2713848A_Latest">Data1!$H$125</definedName>
+    <definedName name="A2713849C">Data1!$G$1:$G$10,Data1!$G$11:$G$125</definedName>
+    <definedName name="A2713849C_Data">Data1!$G$11:$G$125</definedName>
+    <definedName name="A2713849C_Latest">Data1!$G$125</definedName>
+    <definedName name="A2713851R">Data1!$J$1:$J$10,Data1!$J$11:$J$125</definedName>
+    <definedName name="A2713851R_Data">Data1!$J$11:$J$125</definedName>
+    <definedName name="A2713851R_Latest">Data1!$J$125</definedName>
+    <definedName name="A2713852T">Data1!$F$1:$F$10,Data1!$F$11:$F$125</definedName>
+    <definedName name="A2713852T_Data">Data1!$F$11:$F$125</definedName>
+    <definedName name="A2713852T_Latest">Data1!$F$125</definedName>
+    <definedName name="A2713854W">Data1!$I$1:$I$10,Data1!$I$11:$I$125</definedName>
+    <definedName name="A2713854W_Data">Data1!$I$11:$I$125</definedName>
+    <definedName name="A2713854W_Latest">Data1!$I$125</definedName>
+    <definedName name="A83895308K">Data1!$N$1:$N$10,Data1!$N$11:$N$125</definedName>
+    <definedName name="A83895308K_Data">Data1!$N$11:$N$125</definedName>
+    <definedName name="A83895308K_Latest">Data1!$N$125</definedName>
+    <definedName name="A83895309L">Data1!$W$1:$W$10,Data1!$W$11:$W$125</definedName>
+    <definedName name="A83895309L_Data">Data1!$W$11:$W$125</definedName>
+    <definedName name="A83895309L_Latest">Data1!$W$125</definedName>
+    <definedName name="A83895311X">Data1!$Q$1:$Q$10,Data1!$Q$11:$Q$125</definedName>
+    <definedName name="A83895311X_Data">Data1!$Q$11:$Q$125</definedName>
+    <definedName name="A83895311X_Latest">Data1!$Q$125</definedName>
+    <definedName name="A83895312A">Data1!$Z$1:$Z$10,Data1!$Z$11:$Z$125</definedName>
+    <definedName name="A83895312A_Data">Data1!$Z$11:$Z$125</definedName>
+    <definedName name="A83895312A_Latest">Data1!$Z$125</definedName>
+    <definedName name="A83895332K">Data1!$O$1:$O$10,Data1!$O$11:$O$125</definedName>
+    <definedName name="A83895332K_Data">Data1!$O$11:$O$125</definedName>
+    <definedName name="A83895332K_Latest">Data1!$O$125</definedName>
+    <definedName name="A83895333L">Data1!$X$1:$X$10,Data1!$X$11:$X$125</definedName>
+    <definedName name="A83895333L_Data">Data1!$X$11:$X$125</definedName>
+    <definedName name="A83895333L_Latest">Data1!$X$125</definedName>
+    <definedName name="A83895335T">Data1!$R$1:$R$10,Data1!$R$11:$R$125</definedName>
+    <definedName name="A83895335T_Data">Data1!$R$11:$R$125</definedName>
+    <definedName name="A83895335T_Latest">Data1!$R$125</definedName>
+    <definedName name="A83895336V">Data1!$AA$1:$AA$10,Data1!$AA$11:$AA$125</definedName>
+    <definedName name="A83895336V_Data">Data1!$AA$11:$AA$125</definedName>
+    <definedName name="A83895336V_Latest">Data1!$AA$125</definedName>
+    <definedName name="A83895395V">Data1!$P$1:$P$10,Data1!$P$11:$P$125</definedName>
+    <definedName name="A83895395V_Data">Data1!$P$11:$P$125</definedName>
+    <definedName name="A83895395V_Latest">Data1!$P$125</definedName>
+    <definedName name="A83895396W">Data1!$Y$1:$Y$10,Data1!$Y$11:$Y$125</definedName>
+    <definedName name="A83895396W_Data">Data1!$Y$11:$Y$125</definedName>
+    <definedName name="A83895396W_Latest">Data1!$Y$125</definedName>
+    <definedName name="A83895398A">Data1!$S$1:$S$10,Data1!$S$11:$S$125</definedName>
+    <definedName name="A83895398A_Data">Data1!$S$11:$S$125</definedName>
+    <definedName name="A83895398A_Latest">Data1!$S$125</definedName>
+    <definedName name="A83895399C">Data1!$AB$1:$AB$10,Data1!$AB$11:$AB$125</definedName>
+    <definedName name="A83895399C_Data">Data1!$AB$11:$AB$125</definedName>
+    <definedName name="A83895399C_Latest">Data1!$AB$125</definedName>
+    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$125</definedName>
+    <definedName name="Date_Range_Data">Data1!$A$11:$A$125</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -1865,10 +1865,10 @@
         <v>35674</v>
       </c>
       <c r="G12" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H12" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>24</v>
@@ -1897,10 +1897,10 @@
         <v>35674</v>
       </c>
       <c r="G13" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H13" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>24</v>
@@ -1929,10 +1929,10 @@
         <v>35674</v>
       </c>
       <c r="G14" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H14" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>24</v>
@@ -1961,10 +1961,10 @@
         <v>35674</v>
       </c>
       <c r="G15" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H15" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>24</v>
@@ -1993,10 +1993,10 @@
         <v>35674</v>
       </c>
       <c r="G16" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H16" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>24</v>
@@ -2025,10 +2025,10 @@
         <v>35674</v>
       </c>
       <c r="G17" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H17" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>24</v>
@@ -2057,10 +2057,10 @@
         <v>35674</v>
       </c>
       <c r="G18" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H18" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>24</v>
@@ -2089,10 +2089,10 @@
         <v>35674</v>
       </c>
       <c r="G19" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H19" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>24</v>
@@ -2121,10 +2121,10 @@
         <v>35674</v>
       </c>
       <c r="G20" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H20" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>24</v>
@@ -2153,10 +2153,10 @@
         <v>35674</v>
       </c>
       <c r="G21" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H21" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>39</v>
@@ -2185,10 +2185,10 @@
         <v>35674</v>
       </c>
       <c r="G22" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H22" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>39</v>
@@ -2217,10 +2217,10 @@
         <v>35674</v>
       </c>
       <c r="G23" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H23" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>39</v>
@@ -2249,10 +2249,10 @@
         <v>35674</v>
       </c>
       <c r="G24" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H24" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>39</v>
@@ -2281,10 +2281,10 @@
         <v>35674</v>
       </c>
       <c r="G25" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H25" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>39</v>
@@ -2313,10 +2313,10 @@
         <v>35674</v>
       </c>
       <c r="G26" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H26" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>39</v>
@@ -2345,10 +2345,10 @@
         <v>35674</v>
       </c>
       <c r="G27" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H27" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>39</v>
@@ -2377,10 +2377,10 @@
         <v>35674</v>
       </c>
       <c r="G28" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H28" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>39</v>
@@ -2409,10 +2409,10 @@
         <v>35674</v>
       </c>
       <c r="G29" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H29" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>39</v>
@@ -2441,10 +2441,10 @@
         <v>35674</v>
       </c>
       <c r="G30" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H30" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I30" s="10" t="s">
         <v>39</v>
@@ -2473,10 +2473,10 @@
         <v>35674</v>
       </c>
       <c r="G31" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H31" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I31" s="10" t="s">
         <v>39</v>
@@ -2505,10 +2505,10 @@
         <v>35674</v>
       </c>
       <c r="G32" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H32" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I32" s="10" t="s">
         <v>39</v>
@@ -2537,10 +2537,10 @@
         <v>35674</v>
       </c>
       <c r="G33" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H33" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I33" s="10" t="s">
         <v>39</v>
@@ -2569,10 +2569,10 @@
         <v>35674</v>
       </c>
       <c r="G34" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H34" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I34" s="10" t="s">
         <v>39</v>
@@ -2601,10 +2601,10 @@
         <v>35674</v>
       </c>
       <c r="G35" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H35" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I35" s="10" t="s">
         <v>39</v>
@@ -2633,10 +2633,10 @@
         <v>35674</v>
       </c>
       <c r="G36" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H36" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I36" s="10" t="s">
         <v>39</v>
@@ -2665,10 +2665,10 @@
         <v>35674</v>
       </c>
       <c r="G37" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H37" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I37" s="10" t="s">
         <v>39</v>
@@ -2697,10 +2697,10 @@
         <v>35674</v>
       </c>
       <c r="G38" s="9">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H38" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I38" s="10" t="s">
         <v>39</v>
@@ -2762,7 +2762,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB124"/>
+  <dimension ref="A1:AB125"/>
   <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="14.7109375" style="1"/>
@@ -3372,85 +3372,85 @@
         <v>21</v>
       </c>
       <c r="B8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="C8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="D8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="E8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="F8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="G8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="I8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="J8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="K8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="L8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="M8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="N8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="O8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="P8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="Q8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="R8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="S8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="T8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="U8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="V8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="W8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="X8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="Y8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="Z8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AA8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AB8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
@@ -3458,85 +3458,85 @@
         <v>22</v>
       </c>
       <c r="B9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="R9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="S9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="T9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="V9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="W9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="X9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Y9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Z9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AA9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AB9" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
@@ -5871,7 +5871,7 @@
         <v>82.9</v>
       </c>
       <c r="E38" s="8">
-        <v>83.5</v>
+        <v>83.4</v>
       </c>
       <c r="F38" s="8">
         <v>82.3</v>
@@ -5898,7 +5898,7 @@
         <v>0.5</v>
       </c>
       <c r="N38" s="8">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="O38" s="8">
         <v>0.9</v>
@@ -5925,7 +5925,7 @@
         <v>3.5</v>
       </c>
       <c r="W38" s="8">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="X38" s="8">
         <v>4</v>
@@ -5957,7 +5957,7 @@
         <v>84</v>
       </c>
       <c r="E39" s="8">
-        <v>84.1</v>
+        <v>84.2</v>
       </c>
       <c r="F39" s="8">
         <v>83.2</v>
@@ -5984,7 +5984,7 @@
         <v>1.3</v>
       </c>
       <c r="N39" s="8">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O39" s="8">
         <v>1.1000000000000001</v>
@@ -6011,7 +6011,7 @@
         <v>3.6</v>
       </c>
       <c r="W39" s="8">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="X39" s="8">
         <v>3.9</v>
@@ -6070,7 +6070,7 @@
         <v>1</v>
       </c>
       <c r="N40" s="8">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="O40" s="8">
         <v>1.2</v>
@@ -6129,7 +6129,7 @@
         <v>85.7</v>
       </c>
       <c r="E41" s="8">
-        <v>85.9</v>
+        <v>85.8</v>
       </c>
       <c r="F41" s="8">
         <v>85.3</v>
@@ -6156,7 +6156,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="N41" s="8">
-        <v>1.1000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="O41" s="8">
         <v>1.3</v>
@@ -6183,7 +6183,7 @@
         <v>3.9</v>
       </c>
       <c r="W41" s="8">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="X41" s="8">
         <v>4.5</v>
@@ -6242,7 +6242,7 @@
         <v>0.7</v>
       </c>
       <c r="N42" s="8">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O42" s="8">
         <v>1.1000000000000001</v>
@@ -6269,7 +6269,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="W42" s="8">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="X42" s="8">
         <v>4.7</v>
@@ -6355,7 +6355,7 @@
         <v>4.2</v>
       </c>
       <c r="W43" s="8">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="X43" s="8">
         <v>4.7</v>
@@ -6393,7 +6393,7 @@
         <v>87.9</v>
       </c>
       <c r="G44" s="8">
-        <v>88.2</v>
+        <v>88.3</v>
       </c>
       <c r="H44" s="8">
         <v>88.4</v>
@@ -6420,7 +6420,7 @@
         <v>0.9</v>
       </c>
       <c r="P44" s="8">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q44" s="8">
         <v>1</v>
@@ -6447,7 +6447,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="Y44" s="8">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="Z44" s="8">
         <v>4</v>
@@ -6506,7 +6506,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="P45" s="8">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="Q45" s="8">
         <v>1</v>
@@ -6527,7 +6527,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="W45" s="8">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="X45" s="8">
         <v>4.2</v>
@@ -6574,7 +6574,7 @@
         <v>89.9</v>
       </c>
       <c r="J46" s="8">
-        <v>90.1</v>
+        <v>90</v>
       </c>
       <c r="K46" s="8">
         <v>0.8</v>
@@ -6601,7 +6601,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="S46" s="8">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="T46" s="8">
         <v>4</v>
@@ -6628,7 +6628,7 @@
         <v>4.3</v>
       </c>
       <c r="AB46" s="8">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:28" x14ac:dyDescent="0.2">
@@ -6651,7 +6651,7 @@
         <v>90.8</v>
       </c>
       <c r="G47" s="8">
-        <v>90.9</v>
+        <v>90.8</v>
       </c>
       <c r="H47" s="8">
         <v>91</v>
@@ -6660,7 +6660,7 @@
         <v>90.9</v>
       </c>
       <c r="J47" s="8">
-        <v>91</v>
+        <v>90.9</v>
       </c>
       <c r="K47" s="8">
         <v>1</v>
@@ -6678,7 +6678,7 @@
         <v>1</v>
       </c>
       <c r="P47" s="8">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="Q47" s="8">
         <v>1</v>
@@ -6705,7 +6705,7 @@
         <v>4.2</v>
       </c>
       <c r="Y47" s="8">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z47" s="8">
         <v>4</v>
@@ -6714,7 +6714,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="AB47" s="8">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:28" x14ac:dyDescent="0.2">
@@ -6731,16 +6731,16 @@
         <v>91.8</v>
       </c>
       <c r="E48" s="8">
-        <v>91.9</v>
+        <v>91.8</v>
       </c>
       <c r="F48" s="8">
         <v>91.9</v>
       </c>
       <c r="G48" s="8">
-        <v>91.9</v>
+        <v>91.8</v>
       </c>
       <c r="H48" s="8">
-        <v>91.9</v>
+        <v>91.8</v>
       </c>
       <c r="I48" s="8">
         <v>91.8</v>
@@ -6758,7 +6758,7 @@
         <v>1</v>
       </c>
       <c r="N48" s="8">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="O48" s="8">
         <v>1.2</v>
@@ -6767,13 +6767,13 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="Q48" s="8">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="R48" s="8">
         <v>1</v>
       </c>
       <c r="S48" s="8">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T48" s="8">
         <v>3.7</v>
@@ -6785,16 +6785,16 @@
         <v>4</v>
       </c>
       <c r="W48" s="8">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="X48" s="8">
         <v>4.5999999999999996</v>
       </c>
       <c r="Y48" s="8">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Z48" s="8">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AA48" s="8">
         <v>4.3</v>
@@ -6823,7 +6823,7 @@
         <v>92.7</v>
       </c>
       <c r="G49" s="8">
-        <v>92.8</v>
+        <v>92.7</v>
       </c>
       <c r="H49" s="8">
         <v>92.8</v>
@@ -6844,7 +6844,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="N49" s="8">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="O49" s="8">
         <v>0.9</v>
@@ -6853,7 +6853,7 @@
         <v>1</v>
       </c>
       <c r="Q49" s="8">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="R49" s="8">
         <v>1.1000000000000001</v>
@@ -6877,7 +6877,7 @@
         <v>4.3</v>
       </c>
       <c r="Y49" s="8">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z49" s="8">
         <v>3.9</v>
@@ -6936,7 +6936,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="P50" s="8">
-        <v>1.1000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="Q50" s="8">
         <v>1</v>
@@ -6972,7 +6972,7 @@
         <v>4.2</v>
       </c>
       <c r="AB50" s="8">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="51" spans="1:28" x14ac:dyDescent="0.2">
@@ -6995,7 +6995,7 @@
         <v>94.7</v>
       </c>
       <c r="G51" s="8">
-        <v>94.8</v>
+        <v>94.7</v>
       </c>
       <c r="H51" s="8">
         <v>94.7</v>
@@ -7022,7 +7022,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="P51" s="8">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="Q51" s="8">
         <v>1.1000000000000001</v>
@@ -7058,7 +7058,7 @@
         <v>4.2</v>
       </c>
       <c r="AB51" s="8">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="52" spans="1:28" x14ac:dyDescent="0.2">
@@ -7108,7 +7108,7 @@
         <v>1</v>
       </c>
       <c r="P52" s="8">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Q52" s="8">
         <v>1</v>
@@ -7129,16 +7129,16 @@
         <v>4.2</v>
       </c>
       <c r="W52" s="8">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="X52" s="8">
         <v>4</v>
       </c>
       <c r="Y52" s="8">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="Z52" s="8">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="AA52" s="8">
         <v>4.0999999999999996</v>
@@ -7167,7 +7167,7 @@
         <v>96.4</v>
       </c>
       <c r="G53" s="8">
-        <v>96.6</v>
+        <v>96.5</v>
       </c>
       <c r="H53" s="8">
         <v>96.7</v>
@@ -7194,7 +7194,7 @@
         <v>0.8</v>
       </c>
       <c r="P53" s="8">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Q53" s="8">
         <v>1.2</v>
@@ -7280,7 +7280,7 @@
         <v>0.9</v>
       </c>
       <c r="P54" s="8">
-        <v>1.1000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="Q54" s="8">
         <v>1</v>
@@ -7339,7 +7339,7 @@
         <v>98.2</v>
       </c>
       <c r="G55" s="8">
-        <v>98.8</v>
+        <v>98.7</v>
       </c>
       <c r="H55" s="8">
         <v>98.8</v>
@@ -7366,7 +7366,7 @@
         <v>0.9</v>
       </c>
       <c r="P55" s="8">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="Q55" s="8">
         <v>1.1000000000000001</v>
@@ -7452,7 +7452,7 @@
         <v>1.4</v>
       </c>
       <c r="P56" s="8">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q56" s="8">
         <v>0.9</v>
@@ -7565,7 +7565,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="Y57" s="8">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="Z57" s="8">
         <v>3.9</v>
@@ -7737,7 +7737,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="Y59" s="8">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Z59" s="8">
         <v>2.8</v>
@@ -8371,7 +8371,7 @@
         <v>110.3</v>
       </c>
       <c r="G67" s="8">
-        <v>109.3</v>
+        <v>109.4</v>
       </c>
       <c r="H67" s="8">
         <v>109.1</v>
@@ -8398,7 +8398,7 @@
         <v>0.6</v>
       </c>
       <c r="P67" s="8">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q67" s="8">
         <v>0.9</v>
@@ -8425,7 +8425,7 @@
         <v>3.3</v>
       </c>
       <c r="Y67" s="8">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z67" s="8">
         <v>3.8</v>
@@ -8484,7 +8484,7 @@
         <v>0.8</v>
       </c>
       <c r="P68" s="8">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Q68" s="8">
         <v>1</v>
@@ -8769,7 +8769,7 @@
         <v>3.4</v>
       </c>
       <c r="Y71" s="8">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Z71" s="8">
         <v>3.7</v>
@@ -12069,7 +12069,7 @@
         <v>143.19999999999999</v>
       </c>
       <c r="G110" s="8">
-        <v>140.4</v>
+        <v>140.5</v>
       </c>
       <c r="H110" s="8">
         <v>139.69999999999999</v>
@@ -12096,7 +12096,7 @@
         <v>0.6</v>
       </c>
       <c r="P110" s="8">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q110" s="8">
         <v>0.9</v>
@@ -12123,7 +12123,7 @@
         <v>2.4</v>
       </c>
       <c r="Y110" s="8">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Z110" s="8">
         <v>2.9</v>
@@ -12182,7 +12182,7 @@
         <v>0.6</v>
       </c>
       <c r="P111" s="8">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Q111" s="8">
         <v>0.9</v>
@@ -12410,7 +12410,7 @@
         <v>145</v>
       </c>
       <c r="F114" s="8">
-        <v>147.6</v>
+        <v>147.69999999999999</v>
       </c>
       <c r="G114" s="8">
         <v>145.6</v>
@@ -12467,7 +12467,7 @@
         <v>3.1</v>
       </c>
       <c r="Y114" s="8">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Z114" s="8">
         <v>3.9</v>
@@ -12496,16 +12496,16 @@
         <v>147.1</v>
       </c>
       <c r="F115" s="8">
-        <v>149.19999999999999</v>
+        <v>149.1</v>
       </c>
       <c r="G115" s="8">
-        <v>147.5</v>
+        <v>147.6</v>
       </c>
       <c r="H115" s="8">
         <v>146.9</v>
       </c>
       <c r="I115" s="8">
-        <v>149.4</v>
+        <v>149.30000000000001</v>
       </c>
       <c r="J115" s="8">
         <v>147.4</v>
@@ -12523,16 +12523,16 @@
         <v>1.4</v>
       </c>
       <c r="O115" s="8">
-        <v>1.1000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="P115" s="8">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Q115" s="8">
         <v>1.2</v>
       </c>
       <c r="R115" s="8">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="S115" s="8">
         <v>1.1000000000000001</v>
@@ -12553,13 +12553,13 @@
         <v>3.5</v>
       </c>
       <c r="Y115" s="8">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="Z115" s="8">
         <v>4.2</v>
       </c>
       <c r="AA115" s="8">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AB115" s="8">
         <v>4</v>
@@ -12612,13 +12612,13 @@
         <v>1.5</v>
       </c>
       <c r="P116" s="8">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="Q116" s="8">
         <v>1</v>
       </c>
       <c r="R116" s="8">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="S116" s="8">
         <v>1.1000000000000001</v>
@@ -12808,7 +12808,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="X118" s="8">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y118" s="8">
         <v>4.0999999999999996</v>
@@ -12849,7 +12849,7 @@
         <v>152.19999999999999</v>
       </c>
       <c r="I119" s="8">
-        <v>154.6</v>
+        <v>154.5</v>
       </c>
       <c r="J119" s="8">
         <v>152.69999999999999</v>
@@ -12876,7 +12876,7 @@
         <v>0.9</v>
       </c>
       <c r="R119" s="8">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="S119" s="8">
         <v>0.8</v>
@@ -12894,10 +12894,10 @@
         <v>3.5</v>
       </c>
       <c r="X119" s="8">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y119" s="8">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Z119" s="8">
         <v>3.6</v>
@@ -12962,7 +12962,7 @@
         <v>0.8</v>
       </c>
       <c r="R120" s="8">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="S120" s="8">
         <v>0.9</v>
@@ -13107,10 +13107,10 @@
         <v>155.9</v>
       </c>
       <c r="I122" s="8">
-        <v>159</v>
+        <v>159.1</v>
       </c>
       <c r="J122" s="8">
-        <v>156.6</v>
+        <v>156.69999999999999</v>
       </c>
       <c r="K122" s="8">
         <v>0.6</v>
@@ -13134,10 +13134,10 @@
         <v>0.8</v>
       </c>
       <c r="R122" s="8">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="S122" s="8">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="T122" s="8">
         <v>3.3</v>
@@ -13223,7 +13223,7 @@
         <v>0.9</v>
       </c>
       <c r="S123" s="8">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="T123" s="8">
         <v>3.3</v>
@@ -13247,7 +13247,7 @@
         <v>3.3</v>
       </c>
       <c r="AA123" s="8">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AB123" s="8">
         <v>3.5</v>
@@ -13279,7 +13279,7 @@
         <v>158.4</v>
       </c>
       <c r="I124" s="8">
-        <v>162</v>
+        <v>161.80000000000001</v>
       </c>
       <c r="J124" s="8">
         <v>159.19999999999999</v>
@@ -13306,7 +13306,7 @@
         <v>0.8</v>
       </c>
       <c r="R124" s="8">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="S124" s="8">
         <v>0.8</v>
@@ -13333,10 +13333,96 @@
         <v>3.3</v>
       </c>
       <c r="AA124" s="8">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AB124" s="8">
         <v>3.4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A125" s="9">
+        <v>46082</v>
+      </c>
+      <c r="B125" s="8">
+        <v>159.6</v>
+      </c>
+      <c r="C125" s="8">
+        <v>163</v>
+      </c>
+      <c r="D125" s="8">
+        <v>160.30000000000001</v>
+      </c>
+      <c r="E125" s="8">
+        <v>159.69999999999999</v>
+      </c>
+      <c r="F125" s="8">
+        <v>162.69999999999999</v>
+      </c>
+      <c r="G125" s="8">
+        <v>160.4</v>
+      </c>
+      <c r="H125" s="8">
+        <v>159.69999999999999</v>
+      </c>
+      <c r="I125" s="8">
+        <v>162.9</v>
+      </c>
+      <c r="J125" s="8">
+        <v>160.4</v>
+      </c>
+      <c r="K125" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="L125" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="M125" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="N125" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="O125" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P125" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="Q125" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="R125" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="S125" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="T125" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="U125" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="V125" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="W125" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="X125" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="Y125" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="Z125" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="AA125" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="AB125" s="8">
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>
